--- a/data/trans_dic/IP31KM14_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM14_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 32,24</t>
+          <t>19,56; 42,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,74; 40,67</t>
+          <t>15,18; 40,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 33,74</t>
+          <t>20,16; 38,33</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,94; 21,62</t>
+          <t>13,97; 20,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 22,22</t>
+          <t>15,27; 21,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,29; 20,62</t>
+          <t>15,65; 20,22</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 20,32</t>
+          <t>14,38; 25,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 24,4</t>
+          <t>9,88; 20,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,1; 20,78</t>
+          <t>13,44; 21,4</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,41; 20,21</t>
+          <t>16,12; 21,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,24; 22,69</t>
+          <t>15,62; 20,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,18; 20,41</t>
+          <t>16,52; 20,33</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10838</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27555</t>
+          <t>27841</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5841; 17311</t>
+          <t>10509; 22644</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10934; 23726</t>
+          <t>6970; 18737</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19225; 37800</t>
+          <t>20081; 38182</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>113</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>80872</t>
+          <t>79751</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91195</t>
+          <t>78183</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172067</t>
+          <t>157934</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62975; 97666</t>
+          <t>65163; 96926</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>74921; 112264</t>
+          <t>64826; 93290</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>146295; 197372</t>
+          <t>139412; 180166</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21053</t>
+          <t>32045</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33298</t>
+          <t>21734</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54351</t>
+          <t>53778</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14952; 29711</t>
+          <t>23970; 42481</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25068; 44206</t>
+          <t>14533; 30400</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42873; 68015</t>
+          <t>42191; 67157</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>112763</t>
+          <t>127855</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>141210</t>
+          <t>111698</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>253973</t>
+          <t>239553</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93912; 131731</t>
+          <t>110698; 148862</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>120956; 168997</t>
+          <t>96513; 128583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>225952; 285042</t>
+          <t>215569; 265274</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM14_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM14_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan bollería industrial (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27,95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>19,56; 42,16</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15,18; 40,82</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20,16; 38,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18,41%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13,97; 20,78</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15,27; 21,97</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15,65; 20,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>14,38; 25,49</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9,88; 20,66</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13,44; 21,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>16,12; 21,67</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>15,62; 20,82</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16,52; 20,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2989720287128844</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2566553182006392</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2794724403212301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>16059</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11782</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27841</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1956408784441248</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1518427481584697</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.2015719936728062</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>10509; 22644</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6970; 18737</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20081; 38182</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.4215651117626902</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.4081677047140122</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.3832736036581202</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.170984743645075</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1841040376156536</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1772370020757954</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>79751</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>78183</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>157934</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1397078615023563</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1526518864176304</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.156451585951047</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>65163; 96926</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>64826; 93290</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>139412; 180166</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2078062925194444</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2196787923297396</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2021866457551475</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1922458810463268</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1477073485010018</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1713636036800955</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>32045</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>21734</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53778</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1438011845034392</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.09876785170935035</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.1344419547419264</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>23970; 42481</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>14533; 30400</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>42191; 67157</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2548551543829798</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2066061973560548</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2139950082069942</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1861541793670633</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1808258900005351</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1836311780337456</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>127855</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>111698</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>239553</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1611731664784765</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1562433917378493</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.165246008143391</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>110698; 148862</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>96513; 128583</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215569; 265274</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.216740078192304</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2081610095082795</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2033479079951186</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan bollería industrial (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>16059</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>11782</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>27841</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>10509</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>6970</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>20081</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>22644</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>18737</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>38182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>79751</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>78183</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>157934</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>65163</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>64826</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>139412</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>96926</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>93290</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>180166</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>32045</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>21734</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>53778</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>23970</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>14533</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>42191</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>42481</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>30400</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>67157</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>127855</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>111698</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>239553</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>110698</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>96513</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>215569</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>148862</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>128583</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>265274</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>